--- a/docs/points-forklift/production_point_side_analysis_2026-08-13.xlsx
+++ b/docs/points-forklift/production_point_side_analysis_2026-08-13.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Dev\Projects\ApitherapyV2\docs\points-forklift\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6583BE48-FB90-4FCB-9D0C-4E17E1153291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04CA7EFE-BE0F-4F99-ACA9-B536AC6FB778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B53CB321-9345-428E-91FB-E72FE44818FF}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B53CB321-9345-428E-91FB-E72FE44818FF}"/>
   </bookViews>
   <sheets>
     <sheet name="production_point_side_analysis_" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1931" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="786">
   <si>
     <t>id</t>
   </si>
@@ -512,9 +512,6 @@
     <t>GV</t>
   </si>
   <si>
-    <t>expected Midline but geometrically Right</t>
-  </si>
-  <si>
     <t>9V7nJyOIbWM44rp2ZJhJ</t>
   </si>
   <si>
@@ -707,9 +704,6 @@
     <t>Baihui</t>
   </si>
   <si>
-    <t>expected Midline but geometrically Left</t>
-  </si>
-  <si>
     <t>GhFP7hd63X3OnPc24y0r</t>
   </si>
   <si>
@@ -2345,12 +2339,6 @@
     <t>One of the 12 primary bilateral meridians; runs from the big toe, up the inner leg, through the abdomen, to the chest.</t>
   </si>
   <si>
-    <t>Governing Vessel</t>
-  </si>
-  <si>
-    <t>One of the 2 extraordinary meridians; runs along the posterior (back) midline of the body, from the tailbone, up the spine and over the head, to the upper lip.</t>
-  </si>
-  <si>
     <t>Leg Extra Points</t>
   </si>
   <si>
@@ -2373,6 +2361,24 @@
   </si>
   <si>
     <t>Quanliao</t>
+  </si>
+  <si>
+    <t>GV-Back</t>
+  </si>
+  <si>
+    <t>Governing Vessel - Back part</t>
+  </si>
+  <si>
+    <t>One of the 2 extraordinary meridians; runs along the posterior (back) midline of the body, from the tailbone, up the spine to the top of the head.</t>
+  </si>
+  <si>
+    <t>GV-Front</t>
+  </si>
+  <si>
+    <t>Governing Vessel - Front part</t>
+  </si>
+  <si>
+    <t>One of the 2 extraordinary meridians; runs along the antrior (front) midline of the body, from the top of the head, to the upper lip.</t>
   </si>
 </sst>
 </file>
@@ -2959,7 +2965,11 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95364BB2-1D08-4533-980D-723BA5ED0444}" name="טבלה1" displayName="טבלה1" ref="A1:L227" totalsRowShown="0">
-  <autoFilter ref="A1:L227" xr:uid="{95364BB2-1D08-4533-980D-723BA5ED0444}"/>
+  <autoFilter ref="A1:L227" xr:uid="{95364BB2-1D08-4533-980D-723BA5ED0444}">
+    <filterColumn colId="10">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{F3058226-28A8-4335-B97F-4DC407B622EE}" name="id"/>
     <tableColumn id="2" xr3:uid="{38B393D8-8BDD-404D-92AD-DF238E875802}" name="code"/>
@@ -3348,7 +3358,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -3383,7 +3393,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -3418,7 +3428,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -3453,7 +3463,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -3488,7 +3498,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -3523,7 +3533,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -3558,7 +3568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -3593,7 +3603,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -3628,7 +3638,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -3663,7 +3673,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -3698,7 +3708,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>56</v>
       </c>
@@ -3733,7 +3743,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -3768,7 +3778,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -3803,7 +3813,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -3838,7 +3848,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>70</v>
       </c>
@@ -3873,7 +3883,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>73</v>
       </c>
@@ -3908,7 +3918,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>77</v>
       </c>
@@ -3946,7 +3956,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>83</v>
       </c>
@@ -3981,7 +3991,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>87</v>
       </c>
@@ -4016,7 +4026,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>90</v>
       </c>
@@ -4051,7 +4061,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>94</v>
       </c>
@@ -4086,7 +4096,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>97</v>
       </c>
@@ -4121,7 +4131,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>100</v>
       </c>
@@ -4156,7 +4166,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>103</v>
       </c>
@@ -4191,7 +4201,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>106</v>
       </c>
@@ -4226,7 +4236,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>109</v>
       </c>
@@ -4264,7 +4274,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>113</v>
       </c>
@@ -4299,7 +4309,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>116</v>
       </c>
@@ -4334,7 +4344,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>119</v>
       </c>
@@ -4369,7 +4379,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>122</v>
       </c>
@@ -4404,7 +4414,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>125</v>
       </c>
@@ -4439,7 +4449,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>128</v>
       </c>
@@ -4474,7 +4484,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>131</v>
       </c>
@@ -4509,7 +4519,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>134</v>
       </c>
@@ -4544,7 +4554,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>137</v>
       </c>
@@ -4579,7 +4589,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>140</v>
       </c>
@@ -4614,7 +4624,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>143</v>
       </c>
@@ -4649,7 +4659,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>146</v>
       </c>
@@ -4684,7 +4694,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>149</v>
       </c>
@@ -4719,7 +4729,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>152</v>
       </c>
@@ -4754,7 +4764,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>155</v>
       </c>
@@ -4803,7 +4813,7 @@
         <v>161</v>
       </c>
       <c r="E43" t="s">
-        <v>162</v>
+        <v>783</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -4815,27 +4825,27 @@
         <v>7.3201000000000001</v>
       </c>
       <c r="I43" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="J43" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>163</v>
+      </c>
+      <c r="B44" t="s">
         <v>164</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>165</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>166</v>
       </c>
-      <c r="D44" t="s">
-        <v>167</v>
-      </c>
       <c r="E44" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F44">
         <v>-15.3032</v>
@@ -4850,24 +4860,24 @@
         <v>16</v>
       </c>
       <c r="J44" t="s">
+        <v>167</v>
+      </c>
+      <c r="K44" t="s">
+        <v>18</v>
+      </c>
+      <c r="L44" t="s">
         <v>168</v>
       </c>
-      <c r="K44" t="s">
-        <v>18</v>
-      </c>
-      <c r="L44" t="s">
+    </row>
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+      <c r="B45" t="s">
         <v>170</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>171</v>
-      </c>
-      <c r="C45" t="s">
-        <v>172</v>
       </c>
       <c r="D45" t="s">
         <v>26</v>
@@ -4894,15 +4904,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>172</v>
+      </c>
+      <c r="B46" t="s">
         <v>173</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>174</v>
-      </c>
-      <c r="C46" t="s">
-        <v>175</v>
       </c>
       <c r="D46" t="s">
         <v>55</v>
@@ -4929,15 +4939,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>175</v>
+      </c>
+      <c r="B47" t="s">
         <v>176</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>177</v>
-      </c>
-      <c r="C47" t="s">
-        <v>178</v>
       </c>
       <c r="D47" t="s">
         <v>15</v>
@@ -4964,15 +4974,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>178</v>
+      </c>
+      <c r="B48" t="s">
         <v>179</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>180</v>
-      </c>
-      <c r="C48" t="s">
-        <v>181</v>
       </c>
       <c r="D48" t="s">
         <v>30</v>
@@ -4999,15 +5009,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>181</v>
+      </c>
+      <c r="B49" t="s">
         <v>182</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>183</v>
-      </c>
-      <c r="C49" t="s">
-        <v>184</v>
       </c>
       <c r="D49" t="s">
         <v>55</v>
@@ -5034,15 +5044,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>184</v>
+      </c>
+      <c r="B50" t="s">
         <v>185</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>186</v>
-      </c>
-      <c r="C50" t="s">
-        <v>187</v>
       </c>
       <c r="D50" t="s">
         <v>55</v>
@@ -5069,15 +5079,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>187</v>
+      </c>
+      <c r="B51" t="s">
         <v>188</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>189</v>
-      </c>
-      <c r="C51" t="s">
-        <v>190</v>
       </c>
       <c r="D51" t="s">
         <v>30</v>
@@ -5104,15 +5114,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>190</v>
+      </c>
+      <c r="B52" t="s">
         <v>191</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>192</v>
-      </c>
-      <c r="C52" t="s">
-        <v>193</v>
       </c>
       <c r="D52" t="s">
         <v>65</v>
@@ -5139,15 +5149,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" t="s">
         <v>194</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>195</v>
-      </c>
-      <c r="C53" t="s">
-        <v>196</v>
       </c>
       <c r="D53" t="s">
         <v>30</v>
@@ -5174,21 +5184,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>196</v>
+      </c>
+      <c r="B54" t="s">
         <v>197</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>198</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>199</v>
       </c>
-      <c r="D54" t="s">
-        <v>200</v>
-      </c>
       <c r="E54" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F54">
         <v>23.9146</v>
@@ -5209,15 +5219,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>200</v>
+      </c>
+      <c r="B55" t="s">
         <v>201</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>202</v>
-      </c>
-      <c r="C55" t="s">
-        <v>203</v>
       </c>
       <c r="D55" t="s">
         <v>42</v>
@@ -5244,15 +5254,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>203</v>
+      </c>
+      <c r="B56" t="s">
         <v>204</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>205</v>
-      </c>
-      <c r="C56" t="s">
-        <v>206</v>
       </c>
       <c r="D56" t="s">
         <v>42</v>
@@ -5279,15 +5289,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>206</v>
+      </c>
+      <c r="B57" t="s">
         <v>207</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>208</v>
-      </c>
-      <c r="C57" t="s">
-        <v>209</v>
       </c>
       <c r="D57" t="s">
         <v>42</v>
@@ -5314,15 +5324,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>209</v>
+      </c>
+      <c r="B58" t="s">
         <v>210</v>
       </c>
-      <c r="B58" t="s">
-        <v>211</v>
-      </c>
       <c r="C58" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="D58" t="s">
         <v>15</v>
@@ -5349,15 +5359,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
+        <v>212</v>
+      </c>
+      <c r="B59" t="s">
         <v>213</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>214</v>
-      </c>
-      <c r="C59" t="s">
-        <v>215</v>
       </c>
       <c r="D59" t="s">
         <v>42</v>
@@ -5386,13 +5396,13 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>215</v>
+      </c>
+      <c r="B60" t="s">
         <v>216</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>217</v>
-      </c>
-      <c r="C60" t="s">
-        <v>218</v>
       </c>
       <c r="D60" t="s">
         <v>26</v>
@@ -5401,7 +5411,7 @@
         <v>26</v>
       </c>
       <c r="F60">
-        <v>2.9140168704677101</v>
+        <v>-2.9140168704677101</v>
       </c>
       <c r="G60">
         <v>27.9818</v>
@@ -5410,21 +5420,21 @@
         <v>-14.5928</v>
       </c>
       <c r="I60" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="J60" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>218</v>
+      </c>
+      <c r="B61" t="s">
         <v>219</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>220</v>
-      </c>
-      <c r="C61" t="s">
-        <v>221</v>
       </c>
       <c r="D61" t="s">
         <v>42</v>
@@ -5451,15 +5461,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>221</v>
+      </c>
+      <c r="B62" t="s">
         <v>222</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>223</v>
-      </c>
-      <c r="C62" t="s">
-        <v>224</v>
       </c>
       <c r="D62" t="s">
         <v>76</v>
@@ -5488,19 +5498,19 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>224</v>
+      </c>
+      <c r="B63" t="s">
         <v>225</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>226</v>
-      </c>
-      <c r="C63" t="s">
-        <v>227</v>
       </c>
       <c r="D63" t="s">
         <v>161</v>
       </c>
       <c r="E63" t="s">
-        <v>162</v>
+        <v>780</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -5512,24 +5522,21 @@
         <v>-9.5404999999999998</v>
       </c>
       <c r="I63" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="J63" t="s">
         <v>48</v>
       </c>
-      <c r="K63" t="s">
+    </row>
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>227</v>
+      </c>
+      <c r="B64" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
+      <c r="C64" t="s">
         <v>229</v>
-      </c>
-      <c r="B64" t="s">
-        <v>230</v>
-      </c>
-      <c r="C64" t="s">
-        <v>231</v>
       </c>
       <c r="D64" t="s">
         <v>42</v>
@@ -5556,15 +5563,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
+        <v>230</v>
+      </c>
+      <c r="B65" t="s">
+        <v>231</v>
+      </c>
+      <c r="C65" t="s">
         <v>232</v>
-      </c>
-      <c r="B65" t="s">
-        <v>233</v>
-      </c>
-      <c r="C65" t="s">
-        <v>234</v>
       </c>
       <c r="D65" t="s">
         <v>42</v>
@@ -5591,15 +5598,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
+        <v>233</v>
+      </c>
+      <c r="B66" t="s">
+        <v>234</v>
+      </c>
+      <c r="C66" t="s">
         <v>235</v>
-      </c>
-      <c r="B66" t="s">
-        <v>236</v>
-      </c>
-      <c r="C66" t="s">
-        <v>237</v>
       </c>
       <c r="D66" t="s">
         <v>30</v>
@@ -5626,15 +5633,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
+        <v>236</v>
+      </c>
+      <c r="B67" t="s">
+        <v>237</v>
+      </c>
+      <c r="C67" t="s">
         <v>238</v>
-      </c>
-      <c r="B67" t="s">
-        <v>239</v>
-      </c>
-      <c r="C67" t="s">
-        <v>240</v>
       </c>
       <c r="D67" t="s">
         <v>26</v>
@@ -5661,15 +5668,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
+        <v>239</v>
+      </c>
+      <c r="B68" t="s">
+        <v>240</v>
+      </c>
+      <c r="C68" t="s">
         <v>241</v>
-      </c>
-      <c r="B68" t="s">
-        <v>242</v>
-      </c>
-      <c r="C68" t="s">
-        <v>243</v>
       </c>
       <c r="D68" t="s">
         <v>26</v>
@@ -5696,15 +5703,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
+        <v>242</v>
+      </c>
+      <c r="B69" t="s">
+        <v>243</v>
+      </c>
+      <c r="C69" t="s">
         <v>244</v>
-      </c>
-      <c r="B69" t="s">
-        <v>245</v>
-      </c>
-      <c r="C69" t="s">
-        <v>246</v>
       </c>
       <c r="D69" t="s">
         <v>42</v>
@@ -5731,15 +5738,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
+        <v>245</v>
+      </c>
+      <c r="B70" t="s">
+        <v>246</v>
+      </c>
+      <c r="C70" t="s">
         <v>247</v>
-      </c>
-      <c r="B70" t="s">
-        <v>248</v>
-      </c>
-      <c r="C70" t="s">
-        <v>249</v>
       </c>
       <c r="D70" t="s">
         <v>42</v>
@@ -5766,15 +5773,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
+        <v>248</v>
+      </c>
+      <c r="B71" t="s">
+        <v>249</v>
+      </c>
+      <c r="C71" t="s">
         <v>250</v>
-      </c>
-      <c r="B71" t="s">
-        <v>251</v>
-      </c>
-      <c r="C71" t="s">
-        <v>252</v>
       </c>
       <c r="D71" t="s">
         <v>93</v>
@@ -5801,15 +5808,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
+        <v>251</v>
+      </c>
+      <c r="B72" t="s">
+        <v>252</v>
+      </c>
+      <c r="C72" t="s">
         <v>253</v>
-      </c>
-      <c r="B72" t="s">
-        <v>254</v>
-      </c>
-      <c r="C72" t="s">
-        <v>255</v>
       </c>
       <c r="D72" t="s">
         <v>69</v>
@@ -5836,15 +5843,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
+        <v>254</v>
+      </c>
+      <c r="B73" t="s">
+        <v>255</v>
+      </c>
+      <c r="C73" t="s">
         <v>256</v>
-      </c>
-      <c r="B73" t="s">
-        <v>257</v>
-      </c>
-      <c r="C73" t="s">
-        <v>258</v>
       </c>
       <c r="D73" t="s">
         <v>15</v>
@@ -5871,15 +5878,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
+        <v>257</v>
+      </c>
+      <c r="B74" t="s">
+        <v>258</v>
+      </c>
+      <c r="C74" t="s">
         <v>259</v>
-      </c>
-      <c r="B74" t="s">
-        <v>260</v>
-      </c>
-      <c r="C74" t="s">
-        <v>261</v>
       </c>
       <c r="D74" t="s">
         <v>86</v>
@@ -5906,21 +5913,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
+        <v>260</v>
+      </c>
+      <c r="B75" t="s">
+        <v>261</v>
+      </c>
+      <c r="C75" t="s">
         <v>262</v>
       </c>
-      <c r="B75" t="s">
-        <v>263</v>
-      </c>
-      <c r="C75" t="s">
-        <v>264</v>
-      </c>
       <c r="D75" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E75" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F75">
         <v>-25.549800000000001</v>
@@ -5941,15 +5948,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
+        <v>263</v>
+      </c>
+      <c r="B76" t="s">
+        <v>264</v>
+      </c>
+      <c r="C76" t="s">
         <v>265</v>
-      </c>
-      <c r="B76" t="s">
-        <v>266</v>
-      </c>
-      <c r="C76" t="s">
-        <v>267</v>
       </c>
       <c r="D76" t="s">
         <v>65</v>
@@ -5976,15 +5983,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
+        <v>266</v>
+      </c>
+      <c r="B77" t="s">
+        <v>267</v>
+      </c>
+      <c r="C77" t="s">
         <v>268</v>
-      </c>
-      <c r="B77" t="s">
-        <v>269</v>
-      </c>
-      <c r="C77" t="s">
-        <v>270</v>
       </c>
       <c r="D77" t="s">
         <v>69</v>
@@ -6011,18 +6018,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>269</v>
+      </c>
+      <c r="B78" t="s">
+        <v>270</v>
+      </c>
+      <c r="C78" t="s">
         <v>271</v>
       </c>
-      <c r="B78" t="s">
+      <c r="D78" t="s">
         <v>272</v>
-      </c>
-      <c r="C78" t="s">
-        <v>273</v>
-      </c>
-      <c r="D78" t="s">
-        <v>274</v>
       </c>
       <c r="E78" t="s">
         <v>80</v>
@@ -6046,18 +6053,18 @@
         <v>18</v>
       </c>
       <c r="L78" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>274</v>
+      </c>
+      <c r="B79" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
+      <c r="C79" t="s">
         <v>276</v>
-      </c>
-      <c r="B79" t="s">
-        <v>277</v>
-      </c>
-      <c r="C79" t="s">
-        <v>278</v>
       </c>
       <c r="D79" t="s">
         <v>42</v>
@@ -6084,15 +6091,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
+        <v>277</v>
+      </c>
+      <c r="B80" t="s">
+        <v>278</v>
+      </c>
+      <c r="C80" t="s">
         <v>279</v>
-      </c>
-      <c r="B80" t="s">
-        <v>280</v>
-      </c>
-      <c r="C80" t="s">
-        <v>281</v>
       </c>
       <c r="D80" t="s">
         <v>86</v>
@@ -6119,15 +6126,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
+        <v>280</v>
+      </c>
+      <c r="B81" t="s">
+        <v>281</v>
+      </c>
+      <c r="C81" t="s">
         <v>282</v>
-      </c>
-      <c r="B81" t="s">
-        <v>283</v>
-      </c>
-      <c r="C81" t="s">
-        <v>284</v>
       </c>
       <c r="D81" t="s">
         <v>55</v>
@@ -6154,15 +6161,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
+        <v>283</v>
+      </c>
+      <c r="B82" t="s">
+        <v>284</v>
+      </c>
+      <c r="C82" t="s">
         <v>285</v>
-      </c>
-      <c r="B82" t="s">
-        <v>286</v>
-      </c>
-      <c r="C82" t="s">
-        <v>287</v>
       </c>
       <c r="D82" t="s">
         <v>35</v>
@@ -6189,15 +6196,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
+        <v>286</v>
+      </c>
+      <c r="B83" t="s">
+        <v>287</v>
+      </c>
+      <c r="C83" t="s">
         <v>288</v>
-      </c>
-      <c r="B83" t="s">
-        <v>289</v>
-      </c>
-      <c r="C83" t="s">
-        <v>290</v>
       </c>
       <c r="D83" t="s">
         <v>55</v>
@@ -6224,15 +6231,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
+        <v>289</v>
+      </c>
+      <c r="B84" t="s">
+        <v>290</v>
+      </c>
+      <c r="C84" t="s">
         <v>291</v>
-      </c>
-      <c r="B84" t="s">
-        <v>292</v>
-      </c>
-      <c r="C84" t="s">
-        <v>293</v>
       </c>
       <c r="D84" t="s">
         <v>26</v>
@@ -6259,15 +6266,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
+        <v>292</v>
+      </c>
+      <c r="B85" t="s">
+        <v>293</v>
+      </c>
+      <c r="C85" t="s">
         <v>294</v>
-      </c>
-      <c r="B85" t="s">
-        <v>295</v>
-      </c>
-      <c r="C85" t="s">
-        <v>296</v>
       </c>
       <c r="D85" t="s">
         <v>55</v>
@@ -6294,15 +6301,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
+        <v>295</v>
+      </c>
+      <c r="B86" t="s">
+        <v>296</v>
+      </c>
+      <c r="C86" t="s">
         <v>297</v>
-      </c>
-      <c r="B86" t="s">
-        <v>298</v>
-      </c>
-      <c r="C86" t="s">
-        <v>299</v>
       </c>
       <c r="D86" t="s">
         <v>93</v>
@@ -6329,15 +6336,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
+        <v>298</v>
+      </c>
+      <c r="B87" t="s">
+        <v>299</v>
+      </c>
+      <c r="C87" t="s">
         <v>300</v>
-      </c>
-      <c r="B87" t="s">
-        <v>301</v>
-      </c>
-      <c r="C87" t="s">
-        <v>302</v>
       </c>
       <c r="D87" t="s">
         <v>86</v>
@@ -6366,22 +6373,22 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
+        <v>301</v>
+      </c>
+      <c r="B88" t="s">
+        <v>302</v>
+      </c>
+      <c r="C88" t="s">
         <v>303</v>
-      </c>
-      <c r="B88" t="s">
-        <v>304</v>
-      </c>
-      <c r="C88" t="s">
-        <v>305</v>
       </c>
       <c r="D88" t="s">
         <v>162</v>
       </c>
       <c r="E88" t="s">
-        <v>162</v>
+        <v>780</v>
       </c>
       <c r="F88">
-        <v>0.35920000000000002</v>
+        <v>0</v>
       </c>
       <c r="G88">
         <v>61.075299999999999</v>
@@ -6390,24 +6397,21 @@
         <v>-9.2030999999999992</v>
       </c>
       <c r="I88" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="J88" t="s">
         <v>48</v>
       </c>
-      <c r="K88" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>304</v>
+      </c>
+      <c r="B89" t="s">
+        <v>305</v>
+      </c>
+      <c r="C89" t="s">
         <v>306</v>
-      </c>
-      <c r="B89" t="s">
-        <v>307</v>
-      </c>
-      <c r="C89" t="s">
-        <v>308</v>
       </c>
       <c r="D89" t="s">
         <v>69</v>
@@ -6434,15 +6438,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
+        <v>307</v>
+      </c>
+      <c r="B90" t="s">
+        <v>308</v>
+      </c>
+      <c r="C90" t="s">
         <v>309</v>
-      </c>
-      <c r="B90" t="s">
-        <v>310</v>
-      </c>
-      <c r="C90" t="s">
-        <v>311</v>
       </c>
       <c r="D90" t="s">
         <v>30</v>
@@ -6469,15 +6473,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
+        <v>310</v>
+      </c>
+      <c r="B91" t="s">
+        <v>311</v>
+      </c>
+      <c r="C91" t="s">
         <v>312</v>
-      </c>
-      <c r="B91" t="s">
-        <v>313</v>
-      </c>
-      <c r="C91" t="s">
-        <v>314</v>
       </c>
       <c r="D91" t="s">
         <v>69</v>
@@ -6504,15 +6508,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
+        <v>313</v>
+      </c>
+      <c r="B92" t="s">
+        <v>314</v>
+      </c>
+      <c r="C92" t="s">
         <v>315</v>
-      </c>
-      <c r="B92" t="s">
-        <v>316</v>
-      </c>
-      <c r="C92" t="s">
-        <v>317</v>
       </c>
       <c r="D92" t="s">
         <v>30</v>
@@ -6539,15 +6543,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
+        <v>316</v>
+      </c>
+      <c r="B93" t="s">
+        <v>317</v>
+      </c>
+      <c r="C93" t="s">
         <v>318</v>
-      </c>
-      <c r="B93" t="s">
-        <v>319</v>
-      </c>
-      <c r="C93" t="s">
-        <v>320</v>
       </c>
       <c r="D93" t="s">
         <v>15</v>
@@ -6574,15 +6578,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
+        <v>319</v>
+      </c>
+      <c r="B94" t="s">
+        <v>320</v>
+      </c>
+      <c r="C94" t="s">
         <v>321</v>
-      </c>
-      <c r="B94" t="s">
-        <v>322</v>
-      </c>
-      <c r="C94" t="s">
-        <v>323</v>
       </c>
       <c r="D94" t="s">
         <v>46</v>
@@ -6609,18 +6613,18 @@
         <v>18</v>
       </c>
       <c r="L94" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>323</v>
+      </c>
+      <c r="B95" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
+      <c r="C95" t="s">
         <v>325</v>
-      </c>
-      <c r="B95" t="s">
-        <v>326</v>
-      </c>
-      <c r="C95" t="s">
-        <v>327</v>
       </c>
       <c r="D95" t="s">
         <v>42</v>
@@ -6647,15 +6651,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
+        <v>326</v>
+      </c>
+      <c r="B96" t="s">
+        <v>327</v>
+      </c>
+      <c r="C96" t="s">
         <v>328</v>
-      </c>
-      <c r="B96" t="s">
-        <v>329</v>
-      </c>
-      <c r="C96" t="s">
-        <v>330</v>
       </c>
       <c r="D96" t="s">
         <v>42</v>
@@ -6682,15 +6686,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
+        <v>329</v>
+      </c>
+      <c r="B97" t="s">
+        <v>330</v>
+      </c>
+      <c r="C97" t="s">
         <v>331</v>
-      </c>
-      <c r="B97" t="s">
-        <v>332</v>
-      </c>
-      <c r="C97" t="s">
-        <v>333</v>
       </c>
       <c r="D97" t="s">
         <v>42</v>
@@ -6717,15 +6721,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
+        <v>332</v>
+      </c>
+      <c r="B98" t="s">
+        <v>333</v>
+      </c>
+      <c r="C98" t="s">
         <v>334</v>
-      </c>
-      <c r="B98" t="s">
-        <v>335</v>
-      </c>
-      <c r="C98" t="s">
-        <v>336</v>
       </c>
       <c r="D98" t="s">
         <v>86</v>
@@ -6752,15 +6756,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
+        <v>335</v>
+      </c>
+      <c r="B99" t="s">
+        <v>336</v>
+      </c>
+      <c r="C99" t="s">
         <v>337</v>
-      </c>
-      <c r="B99" t="s">
-        <v>338</v>
-      </c>
-      <c r="C99" t="s">
-        <v>339</v>
       </c>
       <c r="D99" t="s">
         <v>69</v>
@@ -6787,15 +6791,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
+        <v>338</v>
+      </c>
+      <c r="B100" t="s">
+        <v>339</v>
+      </c>
+      <c r="C100" t="s">
         <v>340</v>
-      </c>
-      <c r="B100" t="s">
-        <v>341</v>
-      </c>
-      <c r="C100" t="s">
-        <v>342</v>
       </c>
       <c r="D100" t="s">
         <v>93</v>
@@ -6822,15 +6826,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
+        <v>341</v>
+      </c>
+      <c r="B101" t="s">
+        <v>342</v>
+      </c>
+      <c r="C101" t="s">
         <v>343</v>
-      </c>
-      <c r="B101" t="s">
-        <v>344</v>
-      </c>
-      <c r="C101" t="s">
-        <v>345</v>
       </c>
       <c r="D101" t="s">
         <v>42</v>
@@ -6857,15 +6861,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>344</v>
+      </c>
+      <c r="B102" t="s">
+        <v>345</v>
+      </c>
+      <c r="C102" t="s">
         <v>346</v>
-      </c>
-      <c r="B102" t="s">
-        <v>347</v>
-      </c>
-      <c r="C102" t="s">
-        <v>348</v>
       </c>
       <c r="D102" t="s">
         <v>42</v>
@@ -6892,15 +6896,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
+        <v>347</v>
+      </c>
+      <c r="B103" t="s">
+        <v>348</v>
+      </c>
+      <c r="C103" t="s">
         <v>349</v>
-      </c>
-      <c r="B103" t="s">
-        <v>350</v>
-      </c>
-      <c r="C103" t="s">
-        <v>351</v>
       </c>
       <c r="D103" t="s">
         <v>15</v>
@@ -6927,15 +6931,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
+        <v>350</v>
+      </c>
+      <c r="B104" t="s">
+        <v>351</v>
+      </c>
+      <c r="C104" t="s">
         <v>352</v>
-      </c>
-      <c r="B104" t="s">
-        <v>353</v>
-      </c>
-      <c r="C104" t="s">
-        <v>354</v>
       </c>
       <c r="D104" t="s">
         <v>65</v>
@@ -6962,15 +6966,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
+        <v>353</v>
+      </c>
+      <c r="B105" t="s">
+        <v>354</v>
+      </c>
+      <c r="C105" t="s">
         <v>355</v>
-      </c>
-      <c r="B105" t="s">
-        <v>356</v>
-      </c>
-      <c r="C105" t="s">
-        <v>357</v>
       </c>
       <c r="D105" t="s">
         <v>26</v>
@@ -6997,15 +7001,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
+        <v>357</v>
+      </c>
+      <c r="B106" t="s">
+        <v>358</v>
+      </c>
+      <c r="C106" t="s">
         <v>359</v>
-      </c>
-      <c r="B106" t="s">
-        <v>360</v>
-      </c>
-      <c r="C106" t="s">
-        <v>361</v>
       </c>
       <c r="D106" t="s">
         <v>42</v>
@@ -7032,15 +7036,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
+        <v>360</v>
+      </c>
+      <c r="B107" t="s">
+        <v>361</v>
+      </c>
+      <c r="C107" t="s">
         <v>362</v>
-      </c>
-      <c r="B107" t="s">
-        <v>363</v>
-      </c>
-      <c r="C107" t="s">
-        <v>364</v>
       </c>
       <c r="D107" t="s">
         <v>55</v>
@@ -7067,15 +7071,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
+        <v>363</v>
+      </c>
+      <c r="B108" t="s">
+        <v>364</v>
+      </c>
+      <c r="C108" t="s">
         <v>365</v>
-      </c>
-      <c r="B108" t="s">
-        <v>366</v>
-      </c>
-      <c r="C108" t="s">
-        <v>367</v>
       </c>
       <c r="D108" t="s">
         <v>42</v>
@@ -7102,15 +7106,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
+        <v>366</v>
+      </c>
+      <c r="B109" t="s">
+        <v>367</v>
+      </c>
+      <c r="C109" t="s">
         <v>368</v>
-      </c>
-      <c r="B109" t="s">
-        <v>369</v>
-      </c>
-      <c r="C109" t="s">
-        <v>370</v>
       </c>
       <c r="D109" t="s">
         <v>26</v>
@@ -7137,15 +7141,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
+        <v>369</v>
+      </c>
+      <c r="B110" t="s">
+        <v>370</v>
+      </c>
+      <c r="C110" t="s">
         <v>371</v>
-      </c>
-      <c r="B110" t="s">
-        <v>372</v>
-      </c>
-      <c r="C110" t="s">
-        <v>373</v>
       </c>
       <c r="D110" t="s">
         <v>42</v>
@@ -7172,15 +7176,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
+        <v>372</v>
+      </c>
+      <c r="B111" t="s">
+        <v>373</v>
+      </c>
+      <c r="C111" t="s">
         <v>374</v>
-      </c>
-      <c r="B111" t="s">
-        <v>375</v>
-      </c>
-      <c r="C111" t="s">
-        <v>376</v>
       </c>
       <c r="D111" t="s">
         <v>42</v>
@@ -7207,15 +7211,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
+        <v>375</v>
+      </c>
+      <c r="B112" t="s">
+        <v>376</v>
+      </c>
+      <c r="C112" t="s">
         <v>377</v>
-      </c>
-      <c r="B112" t="s">
-        <v>378</v>
-      </c>
-      <c r="C112" t="s">
-        <v>379</v>
       </c>
       <c r="D112" t="s">
         <v>15</v>
@@ -7242,15 +7246,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
+        <v>378</v>
+      </c>
+      <c r="B113" t="s">
+        <v>379</v>
+      </c>
+      <c r="C113" t="s">
         <v>380</v>
-      </c>
-      <c r="B113" t="s">
-        <v>381</v>
-      </c>
-      <c r="C113" t="s">
-        <v>382</v>
       </c>
       <c r="D113" t="s">
         <v>42</v>
@@ -7277,15 +7281,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
+        <v>381</v>
+      </c>
+      <c r="B114" t="s">
+        <v>382</v>
+      </c>
+      <c r="C114" t="s">
         <v>383</v>
-      </c>
-      <c r="B114" t="s">
-        <v>384</v>
-      </c>
-      <c r="C114" t="s">
-        <v>385</v>
       </c>
       <c r="D114" t="s">
         <v>55</v>
@@ -7312,21 +7316,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B115" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C115" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D115" t="s">
         <v>162</v>
       </c>
       <c r="E115" t="s">
-        <v>162</v>
+        <v>780</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -7347,15 +7351,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
+        <v>386</v>
+      </c>
+      <c r="B116" t="s">
+        <v>387</v>
+      </c>
+      <c r="C116" t="s">
         <v>388</v>
-      </c>
-      <c r="B116" t="s">
-        <v>389</v>
-      </c>
-      <c r="C116" t="s">
-        <v>390</v>
       </c>
       <c r="D116" t="s">
         <v>42</v>
@@ -7382,15 +7386,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
+        <v>389</v>
+      </c>
+      <c r="B117" t="s">
+        <v>390</v>
+      </c>
+      <c r="C117" t="s">
         <v>391</v>
-      </c>
-      <c r="B117" t="s">
-        <v>392</v>
-      </c>
-      <c r="C117" t="s">
-        <v>393</v>
       </c>
       <c r="D117" t="s">
         <v>55</v>
@@ -7417,15 +7421,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B118" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C118" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D118" t="s">
         <v>69</v>
@@ -7452,15 +7456,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
+        <v>394</v>
+      </c>
+      <c r="B119" t="s">
+        <v>395</v>
+      </c>
+      <c r="C119" t="s">
         <v>396</v>
-      </c>
-      <c r="B119" t="s">
-        <v>397</v>
-      </c>
-      <c r="C119" t="s">
-        <v>398</v>
       </c>
       <c r="D119" t="s">
         <v>26</v>
@@ -7487,15 +7491,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
+        <v>397</v>
+      </c>
+      <c r="B120" t="s">
+        <v>398</v>
+      </c>
+      <c r="C120" t="s">
         <v>399</v>
-      </c>
-      <c r="B120" t="s">
-        <v>400</v>
-      </c>
-      <c r="C120" t="s">
-        <v>401</v>
       </c>
       <c r="D120" t="s">
         <v>35</v>
@@ -7522,15 +7526,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
+        <v>400</v>
+      </c>
+      <c r="B121" t="s">
+        <v>401</v>
+      </c>
+      <c r="C121" t="s">
         <v>402</v>
-      </c>
-      <c r="B121" t="s">
-        <v>403</v>
-      </c>
-      <c r="C121" t="s">
-        <v>404</v>
       </c>
       <c r="D121" t="s">
         <v>22</v>
@@ -7557,15 +7561,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
+        <v>403</v>
+      </c>
+      <c r="B122" t="s">
+        <v>404</v>
+      </c>
+      <c r="C122" t="s">
         <v>405</v>
-      </c>
-      <c r="B122" t="s">
-        <v>406</v>
-      </c>
-      <c r="C122" t="s">
-        <v>407</v>
       </c>
       <c r="D122" t="s">
         <v>55</v>
@@ -7592,15 +7596,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
+        <v>406</v>
+      </c>
+      <c r="B123" t="s">
+        <v>407</v>
+      </c>
+      <c r="C123" t="s">
         <v>408</v>
-      </c>
-      <c r="B123" t="s">
-        <v>409</v>
-      </c>
-      <c r="C123" t="s">
-        <v>410</v>
       </c>
       <c r="D123" t="s">
         <v>55</v>
@@ -7627,15 +7631,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
+        <v>409</v>
+      </c>
+      <c r="B124" t="s">
+        <v>410</v>
+      </c>
+      <c r="C124" t="s">
         <v>411</v>
-      </c>
-      <c r="B124" t="s">
-        <v>412</v>
-      </c>
-      <c r="C124" t="s">
-        <v>413</v>
       </c>
       <c r="D124" t="s">
         <v>65</v>
@@ -7662,15 +7666,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
+        <v>412</v>
+      </c>
+      <c r="B125" t="s">
+        <v>413</v>
+      </c>
+      <c r="C125" t="s">
         <v>414</v>
-      </c>
-      <c r="B125" t="s">
-        <v>415</v>
-      </c>
-      <c r="C125" t="s">
-        <v>416</v>
       </c>
       <c r="D125" t="s">
         <v>93</v>
@@ -7697,21 +7701,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
+        <v>415</v>
+      </c>
+      <c r="B126" t="s">
+        <v>416</v>
+      </c>
+      <c r="C126" t="s">
         <v>417</v>
       </c>
-      <c r="B126" t="s">
-        <v>418</v>
-      </c>
-      <c r="C126" t="s">
-        <v>419</v>
-      </c>
       <c r="D126" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E126" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F126">
         <v>-20.935700000000001</v>
@@ -7732,15 +7736,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
+        <v>418</v>
+      </c>
+      <c r="B127" t="s">
+        <v>419</v>
+      </c>
+      <c r="C127" t="s">
         <v>420</v>
-      </c>
-      <c r="B127" t="s">
-        <v>421</v>
-      </c>
-      <c r="C127" t="s">
-        <v>422</v>
       </c>
       <c r="D127" t="s">
         <v>30</v>
@@ -7767,15 +7771,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
+        <v>421</v>
+      </c>
+      <c r="B128" t="s">
+        <v>422</v>
+      </c>
+      <c r="C128" t="s">
         <v>423</v>
-      </c>
-      <c r="B128" t="s">
-        <v>424</v>
-      </c>
-      <c r="C128" t="s">
-        <v>425</v>
       </c>
       <c r="D128" t="s">
         <v>42</v>
@@ -7802,15 +7806,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
+        <v>424</v>
+      </c>
+      <c r="B129" t="s">
+        <v>425</v>
+      </c>
+      <c r="C129" t="s">
         <v>426</v>
-      </c>
-      <c r="B129" t="s">
-        <v>427</v>
-      </c>
-      <c r="C129" t="s">
-        <v>428</v>
       </c>
       <c r="D129" t="s">
         <v>42</v>
@@ -7837,15 +7841,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
+        <v>427</v>
+      </c>
+      <c r="B130" t="s">
+        <v>428</v>
+      </c>
+      <c r="C130" t="s">
         <v>429</v>
-      </c>
-      <c r="B130" t="s">
-        <v>430</v>
-      </c>
-      <c r="C130" t="s">
-        <v>431</v>
       </c>
       <c r="D130" t="s">
         <v>42</v>
@@ -7872,15 +7876,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
+        <v>430</v>
+      </c>
+      <c r="B131" t="s">
+        <v>431</v>
+      </c>
+      <c r="C131" t="s">
         <v>432</v>
-      </c>
-      <c r="B131" t="s">
-        <v>433</v>
-      </c>
-      <c r="C131" t="s">
-        <v>434</v>
       </c>
       <c r="D131" t="s">
         <v>15</v>
@@ -7907,15 +7911,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
+        <v>433</v>
+      </c>
+      <c r="B132" t="s">
+        <v>434</v>
+      </c>
+      <c r="C132" t="s">
         <v>435</v>
-      </c>
-      <c r="B132" t="s">
-        <v>436</v>
-      </c>
-      <c r="C132" t="s">
-        <v>437</v>
       </c>
       <c r="D132" t="s">
         <v>42</v>
@@ -7942,15 +7946,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
+        <v>436</v>
+      </c>
+      <c r="B133" t="s">
+        <v>437</v>
+      </c>
+      <c r="C133" t="s">
         <v>438</v>
-      </c>
-      <c r="B133" t="s">
-        <v>439</v>
-      </c>
-      <c r="C133" t="s">
-        <v>440</v>
       </c>
       <c r="D133" t="s">
         <v>86</v>
@@ -7977,15 +7981,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
+        <v>439</v>
+      </c>
+      <c r="B134" t="s">
+        <v>440</v>
+      </c>
+      <c r="C134" t="s">
         <v>441</v>
-      </c>
-      <c r="B134" t="s">
-        <v>442</v>
-      </c>
-      <c r="C134" t="s">
-        <v>443</v>
       </c>
       <c r="D134" t="s">
         <v>15</v>
@@ -8012,15 +8016,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
+        <v>442</v>
+      </c>
+      <c r="B135" t="s">
+        <v>443</v>
+      </c>
+      <c r="C135" t="s">
         <v>444</v>
-      </c>
-      <c r="B135" t="s">
-        <v>445</v>
-      </c>
-      <c r="C135" t="s">
-        <v>446</v>
       </c>
       <c r="D135" t="s">
         <v>55</v>
@@ -8047,15 +8051,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
+        <v>445</v>
+      </c>
+      <c r="B136" t="s">
+        <v>446</v>
+      </c>
+      <c r="C136" t="s">
         <v>447</v>
-      </c>
-      <c r="B136" t="s">
-        <v>448</v>
-      </c>
-      <c r="C136" t="s">
-        <v>449</v>
       </c>
       <c r="D136" t="s">
         <v>15</v>
@@ -8082,15 +8086,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
+        <v>448</v>
+      </c>
+      <c r="B137" t="s">
+        <v>449</v>
+      </c>
+      <c r="C137" t="s">
         <v>450</v>
-      </c>
-      <c r="B137" t="s">
-        <v>451</v>
-      </c>
-      <c r="C137" t="s">
-        <v>452</v>
       </c>
       <c r="D137" t="s">
         <v>30</v>
@@ -8117,15 +8121,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
+        <v>451</v>
+      </c>
+      <c r="B138" t="s">
+        <v>452</v>
+      </c>
+      <c r="C138" t="s">
         <v>453</v>
-      </c>
-      <c r="B138" t="s">
-        <v>454</v>
-      </c>
-      <c r="C138" t="s">
-        <v>455</v>
       </c>
       <c r="D138" t="s">
         <v>55</v>
@@ -8152,18 +8156,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
+        <v>454</v>
+      </c>
+      <c r="B139" t="s">
+        <v>455</v>
+      </c>
+      <c r="C139" t="s">
         <v>456</v>
       </c>
-      <c r="B139" t="s">
+      <c r="D139" t="s">
         <v>457</v>
-      </c>
-      <c r="C139" t="s">
-        <v>458</v>
-      </c>
-      <c r="D139" t="s">
-        <v>459</v>
       </c>
       <c r="E139" t="s">
         <v>69</v>
@@ -8187,18 +8191,18 @@
         <v>18</v>
       </c>
       <c r="L139" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>459</v>
+      </c>
+      <c r="B140" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
+      <c r="C140" t="s">
         <v>461</v>
-      </c>
-      <c r="B140" t="s">
-        <v>462</v>
-      </c>
-      <c r="C140" t="s">
-        <v>463</v>
       </c>
       <c r="D140" t="s">
         <v>42</v>
@@ -8225,15 +8229,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
+        <v>462</v>
+      </c>
+      <c r="B141" t="s">
+        <v>463</v>
+      </c>
+      <c r="C141" t="s">
         <v>464</v>
-      </c>
-      <c r="B141" t="s">
-        <v>465</v>
-      </c>
-      <c r="C141" t="s">
-        <v>466</v>
       </c>
       <c r="D141" t="s">
         <v>15</v>
@@ -8260,15 +8264,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
+        <v>465</v>
+      </c>
+      <c r="B142" t="s">
+        <v>466</v>
+      </c>
+      <c r="C142" t="s">
         <v>467</v>
-      </c>
-      <c r="B142" t="s">
-        <v>468</v>
-      </c>
-      <c r="C142" t="s">
-        <v>469</v>
       </c>
       <c r="D142" t="s">
         <v>42</v>
@@ -8295,15 +8299,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
+        <v>468</v>
+      </c>
+      <c r="B143" t="s">
+        <v>469</v>
+      </c>
+      <c r="C143" t="s">
         <v>470</v>
-      </c>
-      <c r="B143" t="s">
-        <v>471</v>
-      </c>
-      <c r="C143" t="s">
-        <v>472</v>
       </c>
       <c r="D143" t="s">
         <v>86</v>
@@ -8330,15 +8334,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
+        <v>471</v>
+      </c>
+      <c r="B144" t="s">
+        <v>472</v>
+      </c>
+      <c r="C144" t="s">
         <v>473</v>
-      </c>
-      <c r="B144" t="s">
-        <v>474</v>
-      </c>
-      <c r="C144" t="s">
-        <v>475</v>
       </c>
       <c r="D144" t="s">
         <v>55</v>
@@ -8365,21 +8369,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
+        <v>474</v>
+      </c>
+      <c r="B145" t="s">
+        <v>475</v>
+      </c>
+      <c r="C145" t="s">
+        <v>183</v>
+      </c>
+      <c r="D145" t="s">
         <v>476</v>
       </c>
-      <c r="B145" t="s">
-        <v>477</v>
-      </c>
-      <c r="C145" t="s">
-        <v>184</v>
-      </c>
-      <c r="D145" t="s">
-        <v>478</v>
-      </c>
       <c r="E145" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F145">
         <v>-6.9991000000000003</v>
@@ -8400,18 +8404,18 @@
         <v>18</v>
       </c>
       <c r="L145" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>478</v>
+      </c>
+      <c r="B146" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A146" t="s">
+      <c r="C146" t="s">
         <v>480</v>
-      </c>
-      <c r="B146" t="s">
-        <v>481</v>
-      </c>
-      <c r="C146" t="s">
-        <v>482</v>
       </c>
       <c r="D146" t="s">
         <v>30</v>
@@ -8438,15 +8442,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
+        <v>481</v>
+      </c>
+      <c r="B147" t="s">
+        <v>482</v>
+      </c>
+      <c r="C147" t="s">
         <v>483</v>
-      </c>
-      <c r="B147" t="s">
-        <v>484</v>
-      </c>
-      <c r="C147" t="s">
-        <v>485</v>
       </c>
       <c r="D147" t="s">
         <v>65</v>
@@ -8473,15 +8477,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
+        <v>484</v>
+      </c>
+      <c r="B148" t="s">
+        <v>485</v>
+      </c>
+      <c r="C148" t="s">
         <v>486</v>
-      </c>
-      <c r="B148" t="s">
-        <v>487</v>
-      </c>
-      <c r="C148" t="s">
-        <v>488</v>
       </c>
       <c r="D148" t="s">
         <v>26</v>
@@ -8508,15 +8512,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
+        <v>487</v>
+      </c>
+      <c r="B149" t="s">
+        <v>488</v>
+      </c>
+      <c r="C149" t="s">
         <v>489</v>
-      </c>
-      <c r="B149" t="s">
-        <v>490</v>
-      </c>
-      <c r="C149" t="s">
-        <v>491</v>
       </c>
       <c r="D149" t="s">
         <v>42</v>
@@ -8543,15 +8547,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
+        <v>490</v>
+      </c>
+      <c r="B150" t="s">
+        <v>491</v>
+      </c>
+      <c r="C150" t="s">
         <v>492</v>
-      </c>
-      <c r="B150" t="s">
-        <v>493</v>
-      </c>
-      <c r="C150" t="s">
-        <v>494</v>
       </c>
       <c r="D150" t="s">
         <v>30</v>
@@ -8578,15 +8582,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
+        <v>493</v>
+      </c>
+      <c r="B151" t="s">
+        <v>494</v>
+      </c>
+      <c r="C151" t="s">
         <v>495</v>
-      </c>
-      <c r="B151" t="s">
-        <v>496</v>
-      </c>
-      <c r="C151" t="s">
-        <v>497</v>
       </c>
       <c r="D151" t="s">
         <v>69</v>
@@ -8613,15 +8617,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
+        <v>496</v>
+      </c>
+      <c r="B152" t="s">
+        <v>497</v>
+      </c>
+      <c r="C152" t="s">
         <v>498</v>
-      </c>
-      <c r="B152" t="s">
-        <v>499</v>
-      </c>
-      <c r="C152" t="s">
-        <v>500</v>
       </c>
       <c r="D152" t="s">
         <v>65</v>
@@ -8648,15 +8652,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
+        <v>499</v>
+      </c>
+      <c r="B153" t="s">
+        <v>500</v>
+      </c>
+      <c r="C153" t="s">
         <v>501</v>
-      </c>
-      <c r="B153" t="s">
-        <v>502</v>
-      </c>
-      <c r="C153" t="s">
-        <v>503</v>
       </c>
       <c r="D153" t="s">
         <v>69</v>
@@ -8683,15 +8687,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
+        <v>502</v>
+      </c>
+      <c r="B154" t="s">
+        <v>503</v>
+      </c>
+      <c r="C154" t="s">
         <v>504</v>
-      </c>
-      <c r="B154" t="s">
-        <v>505</v>
-      </c>
-      <c r="C154" t="s">
-        <v>506</v>
       </c>
       <c r="D154" t="s">
         <v>42</v>
@@ -8718,15 +8722,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
+        <v>505</v>
+      </c>
+      <c r="B155" t="s">
+        <v>506</v>
+      </c>
+      <c r="C155" t="s">
         <v>507</v>
-      </c>
-      <c r="B155" t="s">
-        <v>508</v>
-      </c>
-      <c r="C155" t="s">
-        <v>509</v>
       </c>
       <c r="D155" t="s">
         <v>55</v>
@@ -8753,21 +8757,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
+        <v>508</v>
+      </c>
+      <c r="B156" t="s">
+        <v>509</v>
+      </c>
+      <c r="C156" t="s">
         <v>510</v>
       </c>
-      <c r="B156" t="s">
-        <v>511</v>
-      </c>
-      <c r="C156" t="s">
-        <v>512</v>
-      </c>
       <c r="D156" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E156" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F156">
         <v>23.910499999999999</v>
@@ -8788,15 +8792,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
+        <v>511</v>
+      </c>
+      <c r="B157" t="s">
+        <v>512</v>
+      </c>
+      <c r="C157" t="s">
         <v>513</v>
-      </c>
-      <c r="B157" t="s">
-        <v>514</v>
-      </c>
-      <c r="C157" t="s">
-        <v>515</v>
       </c>
       <c r="D157" t="s">
         <v>15</v>
@@ -8823,15 +8827,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
+        <v>514</v>
+      </c>
+      <c r="B158" t="s">
+        <v>515</v>
+      </c>
+      <c r="C158" t="s">
         <v>516</v>
-      </c>
-      <c r="B158" t="s">
-        <v>517</v>
-      </c>
-      <c r="C158" t="s">
-        <v>518</v>
       </c>
       <c r="D158" t="s">
         <v>35</v>
@@ -8858,18 +8862,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
+        <v>517</v>
+      </c>
+      <c r="B159" t="s">
+        <v>518</v>
+      </c>
+      <c r="C159" t="s">
         <v>519</v>
       </c>
-      <c r="B159" t="s">
+      <c r="D159" t="s">
         <v>520</v>
-      </c>
-      <c r="C159" t="s">
-        <v>521</v>
-      </c>
-      <c r="D159" t="s">
-        <v>522</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -8893,18 +8897,18 @@
         <v>18</v>
       </c>
       <c r="L159" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>522</v>
+      </c>
+      <c r="B160" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A160" t="s">
+      <c r="C160" t="s">
         <v>524</v>
-      </c>
-      <c r="B160" t="s">
-        <v>525</v>
-      </c>
-      <c r="C160" t="s">
-        <v>526</v>
       </c>
       <c r="D160" t="s">
         <v>26</v>
@@ -8931,15 +8935,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
+        <v>525</v>
+      </c>
+      <c r="B161" t="s">
+        <v>526</v>
+      </c>
+      <c r="C161" t="s">
         <v>527</v>
-      </c>
-      <c r="B161" t="s">
-        <v>528</v>
-      </c>
-      <c r="C161" t="s">
-        <v>529</v>
       </c>
       <c r="D161" t="s">
         <v>69</v>
@@ -8966,18 +8970,18 @@
         <v>18</v>
       </c>
       <c r="L161" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>529</v>
+      </c>
+      <c r="B162" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A162" t="s">
+      <c r="C162" t="s">
         <v>531</v>
-      </c>
-      <c r="B162" t="s">
-        <v>532</v>
-      </c>
-      <c r="C162" t="s">
-        <v>533</v>
       </c>
       <c r="D162" t="s">
         <v>42</v>
@@ -9004,15 +9008,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
+        <v>532</v>
+      </c>
+      <c r="B163" t="s">
+        <v>533</v>
+      </c>
+      <c r="C163" t="s">
         <v>534</v>
-      </c>
-      <c r="B163" t="s">
-        <v>535</v>
-      </c>
-      <c r="C163" t="s">
-        <v>536</v>
       </c>
       <c r="D163" t="s">
         <v>69</v>
@@ -9039,15 +9043,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
+        <v>535</v>
+      </c>
+      <c r="B164" t="s">
+        <v>536</v>
+      </c>
+      <c r="C164" t="s">
         <v>537</v>
-      </c>
-      <c r="B164" t="s">
-        <v>538</v>
-      </c>
-      <c r="C164" t="s">
-        <v>539</v>
       </c>
       <c r="D164" t="s">
         <v>65</v>
@@ -9074,15 +9078,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
+        <v>538</v>
+      </c>
+      <c r="B165" t="s">
+        <v>539</v>
+      </c>
+      <c r="C165" t="s">
         <v>540</v>
-      </c>
-      <c r="B165" t="s">
-        <v>541</v>
-      </c>
-      <c r="C165" t="s">
-        <v>542</v>
       </c>
       <c r="D165" t="s">
         <v>26</v>
@@ -9109,15 +9113,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
+        <v>541</v>
+      </c>
+      <c r="B166" t="s">
+        <v>542</v>
+      </c>
+      <c r="C166" t="s">
         <v>543</v>
-      </c>
-      <c r="B166" t="s">
-        <v>544</v>
-      </c>
-      <c r="C166" t="s">
-        <v>545</v>
       </c>
       <c r="D166" t="s">
         <v>26</v>
@@ -9144,21 +9148,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
+        <v>544</v>
+      </c>
+      <c r="B167" t="s">
+        <v>545</v>
+      </c>
+      <c r="C167" t="s">
         <v>546</v>
       </c>
-      <c r="B167" t="s">
-        <v>547</v>
-      </c>
-      <c r="C167" t="s">
-        <v>548</v>
-      </c>
       <c r="D167" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E167" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F167">
         <v>14.9581</v>
@@ -9179,15 +9183,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
+        <v>547</v>
+      </c>
+      <c r="B168" t="s">
+        <v>548</v>
+      </c>
+      <c r="C168" t="s">
         <v>549</v>
-      </c>
-      <c r="B168" t="s">
-        <v>550</v>
-      </c>
-      <c r="C168" t="s">
-        <v>551</v>
       </c>
       <c r="D168" t="s">
         <v>69</v>
@@ -9214,15 +9218,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
+        <v>550</v>
+      </c>
+      <c r="B169" t="s">
+        <v>551</v>
+      </c>
+      <c r="C169" t="s">
         <v>552</v>
-      </c>
-      <c r="B169" t="s">
-        <v>553</v>
-      </c>
-      <c r="C169" t="s">
-        <v>554</v>
       </c>
       <c r="D169" t="s">
         <v>22</v>
@@ -9249,15 +9253,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
+        <v>553</v>
+      </c>
+      <c r="B170" t="s">
+        <v>554</v>
+      </c>
+      <c r="C170" t="s">
         <v>555</v>
-      </c>
-      <c r="B170" t="s">
-        <v>556</v>
-      </c>
-      <c r="C170" t="s">
-        <v>557</v>
       </c>
       <c r="D170" t="s">
         <v>93</v>
@@ -9284,15 +9288,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
+        <v>556</v>
+      </c>
+      <c r="B171" t="s">
+        <v>557</v>
+      </c>
+      <c r="C171" t="s">
         <v>558</v>
-      </c>
-      <c r="B171" t="s">
-        <v>559</v>
-      </c>
-      <c r="C171" t="s">
-        <v>560</v>
       </c>
       <c r="D171" t="s">
         <v>55</v>
@@ -9319,15 +9323,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
+        <v>559</v>
+      </c>
+      <c r="B172" t="s">
+        <v>560</v>
+      </c>
+      <c r="C172" t="s">
         <v>561</v>
-      </c>
-      <c r="B172" t="s">
-        <v>562</v>
-      </c>
-      <c r="C172" t="s">
-        <v>563</v>
       </c>
       <c r="D172" t="s">
         <v>55</v>
@@ -9354,15 +9358,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
+        <v>562</v>
+      </c>
+      <c r="B173" t="s">
+        <v>563</v>
+      </c>
+      <c r="C173" t="s">
         <v>564</v>
-      </c>
-      <c r="B173" t="s">
-        <v>565</v>
-      </c>
-      <c r="C173" t="s">
-        <v>566</v>
       </c>
       <c r="D173" t="s">
         <v>26</v>
@@ -9389,15 +9393,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
+        <v>565</v>
+      </c>
+      <c r="B174" t="s">
+        <v>566</v>
+      </c>
+      <c r="C174" t="s">
         <v>567</v>
-      </c>
-      <c r="B174" t="s">
-        <v>568</v>
-      </c>
-      <c r="C174" t="s">
-        <v>569</v>
       </c>
       <c r="D174" t="s">
         <v>42</v>
@@ -9424,15 +9428,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
+        <v>568</v>
+      </c>
+      <c r="B175" t="s">
+        <v>569</v>
+      </c>
+      <c r="C175" t="s">
         <v>570</v>
-      </c>
-      <c r="B175" t="s">
-        <v>571</v>
-      </c>
-      <c r="C175" t="s">
-        <v>572</v>
       </c>
       <c r="D175" t="s">
         <v>93</v>
@@ -9459,15 +9463,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
+        <v>571</v>
+      </c>
+      <c r="B176" t="s">
+        <v>572</v>
+      </c>
+      <c r="C176" t="s">
         <v>573</v>
-      </c>
-      <c r="B176" t="s">
-        <v>574</v>
-      </c>
-      <c r="C176" t="s">
-        <v>575</v>
       </c>
       <c r="D176" t="s">
         <v>42</v>
@@ -9494,15 +9498,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
+        <v>574</v>
+      </c>
+      <c r="B177" t="s">
+        <v>575</v>
+      </c>
+      <c r="C177" t="s">
         <v>576</v>
-      </c>
-      <c r="B177" t="s">
-        <v>577</v>
-      </c>
-      <c r="C177" t="s">
-        <v>578</v>
       </c>
       <c r="D177" t="s">
         <v>55</v>
@@ -9529,15 +9533,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
+        <v>577</v>
+      </c>
+      <c r="B178" t="s">
+        <v>578</v>
+      </c>
+      <c r="C178" t="s">
         <v>579</v>
-      </c>
-      <c r="B178" t="s">
-        <v>580</v>
-      </c>
-      <c r="C178" t="s">
-        <v>581</v>
       </c>
       <c r="D178" t="s">
         <v>30</v>
@@ -9564,15 +9568,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
+        <v>580</v>
+      </c>
+      <c r="B179" t="s">
+        <v>581</v>
+      </c>
+      <c r="C179" t="s">
         <v>582</v>
-      </c>
-      <c r="B179" t="s">
-        <v>583</v>
-      </c>
-      <c r="C179" t="s">
-        <v>584</v>
       </c>
       <c r="D179" t="s">
         <v>26</v>
@@ -9599,15 +9603,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
+        <v>583</v>
+      </c>
+      <c r="B180" t="s">
+        <v>584</v>
+      </c>
+      <c r="C180" t="s">
         <v>585</v>
-      </c>
-      <c r="B180" t="s">
-        <v>586</v>
-      </c>
-      <c r="C180" t="s">
-        <v>587</v>
       </c>
       <c r="D180" t="s">
         <v>69</v>
@@ -9636,22 +9640,22 @@
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
+        <v>586</v>
+      </c>
+      <c r="B181" t="s">
+        <v>587</v>
+      </c>
+      <c r="C181" t="s">
         <v>588</v>
-      </c>
-      <c r="B181" t="s">
-        <v>589</v>
-      </c>
-      <c r="C181" t="s">
-        <v>590</v>
       </c>
       <c r="D181" t="s">
         <v>161</v>
       </c>
       <c r="E181" t="s">
-        <v>162</v>
+        <v>780</v>
       </c>
       <c r="F181">
-        <v>-1.0446</v>
+        <v>0</v>
       </c>
       <c r="G181">
         <v>53.646700000000003</v>
@@ -9660,24 +9664,21 @@
         <v>-10.539099999999999</v>
       </c>
       <c r="I181" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="J181" t="s">
         <v>48</v>
       </c>
-      <c r="K181" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
+        <v>589</v>
+      </c>
+      <c r="B182" t="s">
+        <v>590</v>
+      </c>
+      <c r="C182" t="s">
         <v>591</v>
-      </c>
-      <c r="B182" t="s">
-        <v>592</v>
-      </c>
-      <c r="C182" t="s">
-        <v>593</v>
       </c>
       <c r="D182" t="s">
         <v>42</v>
@@ -9704,15 +9705,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
+        <v>592</v>
+      </c>
+      <c r="B183" t="s">
+        <v>593</v>
+      </c>
+      <c r="C183" t="s">
         <v>594</v>
-      </c>
-      <c r="B183" t="s">
-        <v>595</v>
-      </c>
-      <c r="C183" t="s">
-        <v>596</v>
       </c>
       <c r="D183" t="s">
         <v>42</v>
@@ -9739,15 +9740,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
+        <v>595</v>
+      </c>
+      <c r="B184" t="s">
+        <v>596</v>
+      </c>
+      <c r="C184" t="s">
         <v>597</v>
-      </c>
-      <c r="B184" t="s">
-        <v>598</v>
-      </c>
-      <c r="C184" t="s">
-        <v>599</v>
       </c>
       <c r="D184" t="s">
         <v>86</v>
@@ -9774,15 +9775,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
+        <v>598</v>
+      </c>
+      <c r="B185" t="s">
+        <v>599</v>
+      </c>
+      <c r="C185" t="s">
         <v>600</v>
-      </c>
-      <c r="B185" t="s">
-        <v>601</v>
-      </c>
-      <c r="C185" t="s">
-        <v>602</v>
       </c>
       <c r="D185" t="s">
         <v>26</v>
@@ -9809,15 +9810,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
+        <v>603</v>
+      </c>
+      <c r="B186" t="s">
+        <v>604</v>
+      </c>
+      <c r="C186" t="s">
         <v>605</v>
-      </c>
-      <c r="B186" t="s">
-        <v>606</v>
-      </c>
-      <c r="C186" t="s">
-        <v>607</v>
       </c>
       <c r="D186" t="s">
         <v>55</v>
@@ -9844,15 +9845,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
+        <v>606</v>
+      </c>
+      <c r="B187" t="s">
+        <v>607</v>
+      </c>
+      <c r="C187" t="s">
         <v>608</v>
-      </c>
-      <c r="B187" t="s">
-        <v>609</v>
-      </c>
-      <c r="C187" t="s">
-        <v>610</v>
       </c>
       <c r="D187" t="s">
         <v>55</v>
@@ -9879,15 +9880,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
+        <v>609</v>
+      </c>
+      <c r="B188" t="s">
+        <v>610</v>
+      </c>
+      <c r="C188" t="s">
         <v>611</v>
-      </c>
-      <c r="B188" t="s">
-        <v>612</v>
-      </c>
-      <c r="C188" t="s">
-        <v>613</v>
       </c>
       <c r="D188" t="s">
         <v>30</v>
@@ -9914,15 +9915,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
+        <v>612</v>
+      </c>
+      <c r="B189" t="s">
+        <v>613</v>
+      </c>
+      <c r="C189" t="s">
         <v>614</v>
-      </c>
-      <c r="B189" t="s">
-        <v>615</v>
-      </c>
-      <c r="C189" t="s">
-        <v>616</v>
       </c>
       <c r="D189" t="s">
         <v>42</v>
@@ -9949,21 +9950,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
+        <v>615</v>
+      </c>
+      <c r="B190" t="s">
+        <v>616</v>
+      </c>
+      <c r="C190" t="s">
         <v>617</v>
       </c>
-      <c r="B190" t="s">
-        <v>618</v>
-      </c>
-      <c r="C190" t="s">
-        <v>619</v>
-      </c>
       <c r="D190" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E190" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F190">
         <v>-26.328600000000002</v>
@@ -9984,15 +9985,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
+        <v>618</v>
+      </c>
+      <c r="B191" t="s">
+        <v>619</v>
+      </c>
+      <c r="C191" t="s">
         <v>620</v>
-      </c>
-      <c r="B191" t="s">
-        <v>621</v>
-      </c>
-      <c r="C191" t="s">
-        <v>622</v>
       </c>
       <c r="D191" t="s">
         <v>69</v>
@@ -10019,15 +10020,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
+        <v>621</v>
+      </c>
+      <c r="B192" t="s">
+        <v>622</v>
+      </c>
+      <c r="C192" t="s">
         <v>623</v>
-      </c>
-      <c r="B192" t="s">
-        <v>624</v>
-      </c>
-      <c r="C192" t="s">
-        <v>625</v>
       </c>
       <c r="D192" t="s">
         <v>26</v>
@@ -10054,15 +10055,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
+        <v>624</v>
+      </c>
+      <c r="B193" t="s">
+        <v>625</v>
+      </c>
+      <c r="C193" t="s">
         <v>626</v>
-      </c>
-      <c r="B193" t="s">
-        <v>627</v>
-      </c>
-      <c r="C193" t="s">
-        <v>628</v>
       </c>
       <c r="D193" t="s">
         <v>42</v>
@@ -10089,15 +10090,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
+        <v>627</v>
+      </c>
+      <c r="B194" t="s">
+        <v>628</v>
+      </c>
+      <c r="C194" t="s">
         <v>629</v>
-      </c>
-      <c r="B194" t="s">
-        <v>630</v>
-      </c>
-      <c r="C194" t="s">
-        <v>631</v>
       </c>
       <c r="D194" t="s">
         <v>69</v>
@@ -10124,15 +10125,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
+        <v>630</v>
+      </c>
+      <c r="B195" t="s">
+        <v>631</v>
+      </c>
+      <c r="C195" t="s">
         <v>632</v>
-      </c>
-      <c r="B195" t="s">
-        <v>633</v>
-      </c>
-      <c r="C195" t="s">
-        <v>634</v>
       </c>
       <c r="D195" t="s">
         <v>26</v>
@@ -10159,15 +10160,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
+        <v>633</v>
+      </c>
+      <c r="B196" t="s">
+        <v>634</v>
+      </c>
+      <c r="C196" t="s">
         <v>635</v>
-      </c>
-      <c r="B196" t="s">
-        <v>636</v>
-      </c>
-      <c r="C196" t="s">
-        <v>637</v>
       </c>
       <c r="D196" t="s">
         <v>26</v>
@@ -10194,15 +10195,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
+        <v>636</v>
+      </c>
+      <c r="B197" t="s">
+        <v>637</v>
+      </c>
+      <c r="C197" t="s">
         <v>638</v>
-      </c>
-      <c r="B197" t="s">
-        <v>639</v>
-      </c>
-      <c r="C197" t="s">
-        <v>640</v>
       </c>
       <c r="D197" t="s">
         <v>26</v>
@@ -10229,15 +10230,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
+        <v>639</v>
+      </c>
+      <c r="B198" t="s">
+        <v>640</v>
+      </c>
+      <c r="C198" t="s">
         <v>641</v>
-      </c>
-      <c r="B198" t="s">
-        <v>642</v>
-      </c>
-      <c r="C198" t="s">
-        <v>643</v>
       </c>
       <c r="D198" t="s">
         <v>93</v>
@@ -10264,21 +10265,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
+        <v>642</v>
+      </c>
+      <c r="B199" t="s">
+        <v>643</v>
+      </c>
+      <c r="C199" t="s">
         <v>644</v>
       </c>
-      <c r="B199" t="s">
-        <v>645</v>
-      </c>
-      <c r="C199" t="s">
-        <v>646</v>
-      </c>
       <c r="D199" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E199" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F199">
         <v>23.255500000000001</v>
@@ -10301,45 +10302,45 @@
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
+        <v>645</v>
+      </c>
+      <c r="B200" t="s">
+        <v>646</v>
+      </c>
+      <c r="C200" t="s">
         <v>647</v>
       </c>
-      <c r="B200" t="s">
-        <v>648</v>
-      </c>
-      <c r="C200" t="s">
-        <v>649</v>
-      </c>
       <c r="D200" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E200" t="s">
         <v>69</v>
       </c>
       <c r="F200">
-        <v>12.102518270498001</v>
+        <v>-13.493720108419801</v>
       </c>
       <c r="G200">
-        <v>50.953549852974099</v>
+        <v>51.216235653002499</v>
       </c>
       <c r="H200">
-        <v>-8.7568803784056808</v>
+        <v>-5.7102962403533502</v>
       </c>
       <c r="I200" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="J200" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
+        <v>648</v>
+      </c>
+      <c r="B201" t="s">
+        <v>649</v>
+      </c>
+      <c r="C201" t="s">
         <v>650</v>
-      </c>
-      <c r="B201" t="s">
-        <v>651</v>
-      </c>
-      <c r="C201" t="s">
-        <v>652</v>
       </c>
       <c r="D201" t="s">
         <v>15</v>
@@ -10366,15 +10367,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
+        <v>651</v>
+      </c>
+      <c r="B202" t="s">
+        <v>652</v>
+      </c>
+      <c r="C202" t="s">
         <v>653</v>
-      </c>
-      <c r="B202" t="s">
-        <v>654</v>
-      </c>
-      <c r="C202" t="s">
-        <v>655</v>
       </c>
       <c r="D202" t="s">
         <v>15</v>
@@ -10401,15 +10402,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
+        <v>654</v>
+      </c>
+      <c r="B203" t="s">
+        <v>655</v>
+      </c>
+      <c r="C203" t="s">
         <v>656</v>
-      </c>
-      <c r="B203" t="s">
-        <v>657</v>
-      </c>
-      <c r="C203" t="s">
-        <v>658</v>
       </c>
       <c r="D203" t="s">
         <v>76</v>
@@ -10436,15 +10437,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B204" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C204" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D204" t="s">
         <v>30</v>
@@ -10471,15 +10472,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
+        <v>658</v>
+      </c>
+      <c r="B205" t="s">
+        <v>659</v>
+      </c>
+      <c r="C205" t="s">
         <v>660</v>
-      </c>
-      <c r="B205" t="s">
-        <v>661</v>
-      </c>
-      <c r="C205" t="s">
-        <v>662</v>
       </c>
       <c r="D205" t="s">
         <v>26</v>
@@ -10506,15 +10507,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
+        <v>661</v>
+      </c>
+      <c r="B206" t="s">
+        <v>662</v>
+      </c>
+      <c r="C206" t="s">
         <v>663</v>
-      </c>
-      <c r="B206" t="s">
-        <v>664</v>
-      </c>
-      <c r="C206" t="s">
-        <v>665</v>
       </c>
       <c r="D206" t="s">
         <v>35</v>
@@ -10541,15 +10542,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
+        <v>664</v>
+      </c>
+      <c r="B207" t="s">
+        <v>665</v>
+      </c>
+      <c r="C207" t="s">
         <v>666</v>
-      </c>
-      <c r="B207" t="s">
-        <v>667</v>
-      </c>
-      <c r="C207" t="s">
-        <v>668</v>
       </c>
       <c r="D207" t="s">
         <v>42</v>
@@ -10576,15 +10577,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
+        <v>667</v>
+      </c>
+      <c r="B208" t="s">
+        <v>668</v>
+      </c>
+      <c r="C208" t="s">
         <v>669</v>
-      </c>
-      <c r="B208" t="s">
-        <v>670</v>
-      </c>
-      <c r="C208" t="s">
-        <v>671</v>
       </c>
       <c r="D208" t="s">
         <v>30</v>
@@ -10611,15 +10612,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
+        <v>670</v>
+      </c>
+      <c r="B209" t="s">
+        <v>671</v>
+      </c>
+      <c r="C209" t="s">
         <v>672</v>
-      </c>
-      <c r="B209" t="s">
-        <v>673</v>
-      </c>
-      <c r="C209" t="s">
-        <v>674</v>
       </c>
       <c r="D209" t="s">
         <v>26</v>
@@ -10646,15 +10647,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
+        <v>673</v>
+      </c>
+      <c r="B210" t="s">
+        <v>674</v>
+      </c>
+      <c r="C210" t="s">
         <v>675</v>
-      </c>
-      <c r="B210" t="s">
-        <v>676</v>
-      </c>
-      <c r="C210" t="s">
-        <v>677</v>
       </c>
       <c r="D210" t="s">
         <v>86</v>
@@ -10681,15 +10682,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
+        <v>676</v>
+      </c>
+      <c r="B211" t="s">
+        <v>677</v>
+      </c>
+      <c r="C211" t="s">
         <v>678</v>
-      </c>
-      <c r="B211" t="s">
-        <v>679</v>
-      </c>
-      <c r="C211" t="s">
-        <v>680</v>
       </c>
       <c r="D211" t="s">
         <v>15</v>
@@ -10716,15 +10717,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
+        <v>679</v>
+      </c>
+      <c r="B212" t="s">
+        <v>680</v>
+      </c>
+      <c r="C212" t="s">
         <v>681</v>
-      </c>
-      <c r="B212" t="s">
-        <v>682</v>
-      </c>
-      <c r="C212" t="s">
-        <v>683</v>
       </c>
       <c r="D212" t="s">
         <v>42</v>
@@ -10751,15 +10752,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
+        <v>682</v>
+      </c>
+      <c r="B213" t="s">
+        <v>683</v>
+      </c>
+      <c r="C213" t="s">
         <v>684</v>
-      </c>
-      <c r="B213" t="s">
-        <v>685</v>
-      </c>
-      <c r="C213" t="s">
-        <v>686</v>
       </c>
       <c r="D213" t="s">
         <v>42</v>
@@ -10786,15 +10787,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
+        <v>685</v>
+      </c>
+      <c r="B214" t="s">
+        <v>686</v>
+      </c>
+      <c r="C214" t="s">
         <v>687</v>
-      </c>
-      <c r="B214" t="s">
-        <v>688</v>
-      </c>
-      <c r="C214" t="s">
-        <v>689</v>
       </c>
       <c r="D214" t="s">
         <v>30</v>
@@ -10821,15 +10822,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
+        <v>688</v>
+      </c>
+      <c r="B215" t="s">
+        <v>689</v>
+      </c>
+      <c r="C215" t="s">
         <v>690</v>
-      </c>
-      <c r="B215" t="s">
-        <v>691</v>
-      </c>
-      <c r="C215" t="s">
-        <v>692</v>
       </c>
       <c r="D215" t="s">
         <v>30</v>
@@ -10856,21 +10857,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
+        <v>691</v>
+      </c>
+      <c r="B216" t="s">
+        <v>692</v>
+      </c>
+      <c r="C216" t="s">
         <v>693</v>
       </c>
-      <c r="B216" t="s">
-        <v>694</v>
-      </c>
-      <c r="C216" t="s">
-        <v>695</v>
-      </c>
       <c r="D216" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E216" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F216">
         <v>-25.922899999999998</v>
@@ -10891,15 +10892,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
+        <v>694</v>
+      </c>
+      <c r="B217" t="s">
+        <v>695</v>
+      </c>
+      <c r="C217" t="s">
         <v>696</v>
-      </c>
-      <c r="B217" t="s">
-        <v>697</v>
-      </c>
-      <c r="C217" t="s">
-        <v>698</v>
       </c>
       <c r="D217" t="s">
         <v>93</v>
@@ -10926,15 +10927,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
+        <v>697</v>
+      </c>
+      <c r="B218" t="s">
+        <v>698</v>
+      </c>
+      <c r="C218" t="s">
         <v>699</v>
-      </c>
-      <c r="B218" t="s">
-        <v>700</v>
-      </c>
-      <c r="C218" t="s">
-        <v>701</v>
       </c>
       <c r="D218" t="s">
         <v>65</v>
@@ -10961,15 +10962,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
+        <v>700</v>
+      </c>
+      <c r="B219" t="s">
+        <v>701</v>
+      </c>
+      <c r="C219" t="s">
         <v>702</v>
-      </c>
-      <c r="B219" t="s">
-        <v>703</v>
-      </c>
-      <c r="C219" t="s">
-        <v>704</v>
       </c>
       <c r="D219" t="s">
         <v>76</v>
@@ -10996,18 +10997,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
+        <v>703</v>
+      </c>
+      <c r="B220" t="s">
+        <v>704</v>
+      </c>
+      <c r="C220" t="s">
         <v>705</v>
       </c>
-      <c r="B220" t="s">
-        <v>706</v>
-      </c>
-      <c r="C220" t="s">
-        <v>707</v>
-      </c>
       <c r="D220" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E220" t="s">
         <v>69</v>
@@ -11031,21 +11032,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
+        <v>706</v>
+      </c>
+      <c r="B221" t="s">
+        <v>707</v>
+      </c>
+      <c r="C221" t="s">
         <v>708</v>
       </c>
-      <c r="B221" t="s">
-        <v>709</v>
-      </c>
-      <c r="C221" t="s">
-        <v>710</v>
-      </c>
       <c r="D221" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E221" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F221">
         <v>-14.216799999999999</v>
@@ -11066,15 +11067,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
+        <v>709</v>
+      </c>
+      <c r="B222" t="s">
+        <v>710</v>
+      </c>
+      <c r="C222" t="s">
         <v>711</v>
-      </c>
-      <c r="B222" t="s">
-        <v>712</v>
-      </c>
-      <c r="C222" t="s">
-        <v>713</v>
       </c>
       <c r="D222" t="s">
         <v>93</v>
@@ -11101,15 +11102,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
+        <v>712</v>
+      </c>
+      <c r="B223" t="s">
+        <v>713</v>
+      </c>
+      <c r="C223" t="s">
         <v>714</v>
-      </c>
-      <c r="B223" t="s">
-        <v>715</v>
-      </c>
-      <c r="C223" t="s">
-        <v>716</v>
       </c>
       <c r="D223" t="s">
         <v>76</v>
@@ -11136,18 +11137,18 @@
         <v>18</v>
       </c>
       <c r="L223" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>716</v>
+      </c>
+      <c r="B224" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A224" t="s">
+      <c r="C224" t="s">
         <v>718</v>
-      </c>
-      <c r="B224" t="s">
-        <v>719</v>
-      </c>
-      <c r="C224" t="s">
-        <v>720</v>
       </c>
       <c r="D224" t="s">
         <v>55</v>
@@ -11174,15 +11175,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
+        <v>719</v>
+      </c>
+      <c r="B225" t="s">
+        <v>720</v>
+      </c>
+      <c r="C225" t="s">
         <v>721</v>
-      </c>
-      <c r="B225" t="s">
-        <v>722</v>
-      </c>
-      <c r="C225" t="s">
-        <v>723</v>
       </c>
       <c r="D225" t="s">
         <v>69</v>
@@ -11209,15 +11210,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
+        <v>722</v>
+      </c>
+      <c r="B226" t="s">
+        <v>723</v>
+      </c>
+      <c r="C226" t="s">
         <v>724</v>
-      </c>
-      <c r="B226" t="s">
-        <v>725</v>
-      </c>
-      <c r="C226" t="s">
-        <v>726</v>
       </c>
       <c r="D226" t="s">
         <v>22</v>
@@ -11244,15 +11245,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
+        <v>725</v>
+      </c>
+      <c r="B227" t="s">
+        <v>726</v>
+      </c>
+      <c r="C227" t="s">
         <v>727</v>
-      </c>
-      <c r="B227" t="s">
-        <v>728</v>
-      </c>
-      <c r="C227" t="s">
-        <v>729</v>
       </c>
       <c r="D227" t="s">
         <v>93</v>
@@ -11289,7 +11290,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940E8828-E742-48F4-8705-103F28F4C8D1}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -11302,22 +11303,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>733</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="57" x14ac:dyDescent="0.2">
@@ -11325,13 +11326,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>736</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>738</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>17</v>
@@ -11343,13 +11344,13 @@
         <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>17</v>
@@ -11361,13 +11362,13 @@
         <v>26</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>17</v>
@@ -11379,13 +11380,13 @@
         <v>30</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>17</v>
@@ -11397,13 +11398,13 @@
         <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>17</v>
@@ -11415,13 +11416,13 @@
         <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>17</v>
@@ -11433,39 +11434,39 @@
         <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>755</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
@@ -11473,19 +11474,19 @@
         <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>759</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>760</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="57" x14ac:dyDescent="0.2">
@@ -11493,16 +11494,16 @@
         <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -11511,13 +11512,13 @@
         <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>17</v>
@@ -11529,13 +11530,13 @@
         <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>17</v>
@@ -11547,13 +11548,13 @@
         <v>76</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>17</v>
@@ -11565,13 +11566,13 @@
         <v>86</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>17</v>
@@ -11583,90 +11584,108 @@
         <v>93</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>780</v>
+      </c>
+      <c r="B17" t="s">
+        <v>781</v>
+      </c>
+      <c r="C17" t="s">
+        <v>782</v>
+      </c>
+      <c r="D17" t="s">
+        <v>736</v>
+      </c>
+      <c r="E17" t="s">
+        <v>754</v>
+      </c>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>783</v>
+      </c>
+      <c r="B18" t="s">
+        <v>784</v>
+      </c>
+      <c r="C18" t="s">
+        <v>785</v>
+      </c>
+      <c r="D18" t="s">
+        <v>736</v>
+      </c>
+      <c r="E18" t="s">
+        <v>758</v>
+      </c>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6" ht="57" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>772</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" ht="57" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" ht="57" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>478</v>
+        <v>199</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>751</v>
+        <v>736</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
